--- a/InputData/cpi.xlsx
+++ b/InputData/cpi.xlsx
@@ -1,27 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mengpin.ge\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-hongkong-develop\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_AF8BA3F71FAE3818F19A5FA0D18A4D8271DD9412" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EBE68E1-0A35-441E-9C13-8DD4B5F8F5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12210" yWindow="1845" windowWidth="15645" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="76">
   <si>
     <t>CPI Consumer Price Index</t>
   </si>
@@ -91,163 +93,172 @@
     <t>Dec.</t>
   </si>
   <si>
-    <t>1968.............................................................................     .</t>
-  </si>
-  <si>
     <t>–</t>
   </si>
   <si>
-    <t>1969.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1970.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1971.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1972.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1973.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1974.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1975.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1976.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1977.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1978.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1979.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1980.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1981.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1982.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1983.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1984.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1985.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1986.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1987.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1988.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1989.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1990.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1991.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1992.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1993.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1994.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1995.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1996.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1997.............................................................................      .</t>
-  </si>
-  <si>
-    <t>1998.............................................................................     .</t>
-  </si>
-  <si>
-    <t>1999.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2000.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2001.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2002.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2003.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2004.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2005.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2006.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2007.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2008.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2009.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2010.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2011.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2012.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2013.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2014.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2015.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2016.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2017.............................................................................     .</t>
-  </si>
-  <si>
-    <t>2018.............................................................................     .</t>
-  </si>
-  <si>
-    <t>https://www.bls.gov/cpi/tables/supplemental-files/historical-cpi-u-201812.pdf</t>
+    <t>https://www.bls.gov/cpi/tables/supplemental-files/historical-cpi-u-201912.pdf</t>
+  </si>
+  <si>
+    <t>1968............................................................................. .</t>
+  </si>
+  <si>
+    <t>1969............................................................................. .</t>
+  </si>
+  <si>
+    <t>1970............................................................................. .</t>
+  </si>
+  <si>
+    <t>1971............................................................................. .</t>
+  </si>
+  <si>
+    <t>1972............................................................................. .</t>
+  </si>
+  <si>
+    <t>1973............................................................................. .</t>
+  </si>
+  <si>
+    <t>1974............................................................................. .</t>
+  </si>
+  <si>
+    <t>1975............................................................................. .</t>
+  </si>
+  <si>
+    <t>1976............................................................................. .</t>
+  </si>
+  <si>
+    <t>1977............................................................................. .</t>
+  </si>
+  <si>
+    <t>1978............................................................................. .</t>
+  </si>
+  <si>
+    <t>1979............................................................................. .</t>
+  </si>
+  <si>
+    <t>1980............................................................................. .</t>
+  </si>
+  <si>
+    <t>1981............................................................................. .</t>
+  </si>
+  <si>
+    <t>1982............................................................................. .</t>
+  </si>
+  <si>
+    <t>1983............................................................................. .</t>
+  </si>
+  <si>
+    <t>1984............................................................................. .</t>
+  </si>
+  <si>
+    <t>1985............................................................................. .</t>
+  </si>
+  <si>
+    <t>1986............................................................................. .</t>
+  </si>
+  <si>
+    <t>1987............................................................................. .</t>
+  </si>
+  <si>
+    <t>1988............................................................................. .</t>
+  </si>
+  <si>
+    <t>1989............................................................................. .</t>
+  </si>
+  <si>
+    <t>1990............................................................................. .</t>
+  </si>
+  <si>
+    <t>1991............................................................................. .</t>
+  </si>
+  <si>
+    <t>1992............................................................................. .</t>
+  </si>
+  <si>
+    <t>1993............................................................................. .</t>
+  </si>
+  <si>
+    <t>1994............................................................................. .</t>
+  </si>
+  <si>
+    <t>1995............................................................................. .</t>
+  </si>
+  <si>
+    <t>1996............................................................................. .</t>
+  </si>
+  <si>
+    <t>1997............................................................................. .</t>
+  </si>
+  <si>
+    <t>1998............................................................................. .</t>
+  </si>
+  <si>
+    <t>1999............................................................................. .</t>
+  </si>
+  <si>
+    <t>2000............................................................................. .</t>
+  </si>
+  <si>
+    <t>2001............................................................................. .</t>
+  </si>
+  <si>
+    <t>2002............................................................................. .</t>
+  </si>
+  <si>
+    <t>2003............................................................................. .</t>
+  </si>
+  <si>
+    <t>2004............................................................................. .</t>
+  </si>
+  <si>
+    <t>2005............................................................................. .</t>
+  </si>
+  <si>
+    <t>2006............................................................................. .</t>
+  </si>
+  <si>
+    <t>2007............................................................................. .</t>
+  </si>
+  <si>
+    <t>2008............................................................................. .</t>
+  </si>
+  <si>
+    <t>2009............................................................................. .</t>
+  </si>
+  <si>
+    <t>2010............................................................................. .</t>
+  </si>
+  <si>
+    <t>2011............................................................................. .</t>
+  </si>
+  <si>
+    <t>2012............................................................................. .</t>
+  </si>
+  <si>
+    <t>2013............................................................................. .</t>
+  </si>
+  <si>
+    <t>2014............................................................................. .</t>
+  </si>
+  <si>
+    <t>2015............................................................................. .</t>
+  </si>
+  <si>
+    <t>2016............................................................................. .</t>
+  </si>
+  <si>
+    <t>2017............................................................................. .</t>
+  </si>
+  <si>
+    <t>2018............................................................................. .</t>
+  </si>
+  <si>
+    <t>2019............................................................................. .</t>
+  </si>
+  <si>
+    <t>2020............................................................................. .</t>
+  </si>
+  <si>
+    <t>2021............................................................................. .</t>
   </si>
 </sst>
 </file>
@@ -675,7 +686,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -685,7 +696,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -724,7 +735,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="14" max="14" width="10.5703125" customWidth="1"/>
@@ -779,13 +790,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
         <v>34.799999999999997</v>
@@ -799,13 +810,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>36.700000000000003</v>
@@ -819,13 +830,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>38.799999999999997</v>
@@ -839,13 +850,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>40.5</v>
@@ -859,13 +870,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>41.8</v>
@@ -879,13 +890,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11">
         <v>44.4</v>
@@ -899,13 +910,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12">
         <v>49.3</v>
@@ -919,13 +930,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13">
         <v>53.8</v>
@@ -939,13 +950,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>56.9</v>
@@ -959,13 +970,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15">
         <v>60.6</v>
@@ -979,13 +990,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <v>65.2</v>
@@ -999,13 +1010,13 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17">
         <v>72.599999999999994</v>
@@ -1019,13 +1030,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18">
         <v>82.4</v>
@@ -1039,13 +1050,13 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19">
         <v>90.9</v>
@@ -1059,13 +1070,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>96.5</v>
@@ -1079,13 +1090,13 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>99.6</v>
@@ -1099,7 +1110,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22">
         <v>102.9</v>
@@ -1119,7 +1130,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23">
         <v>106.6</v>
@@ -1139,7 +1150,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24">
         <v>109.1</v>
@@ -1159,7 +1170,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25">
         <v>112.4</v>
@@ -1179,7 +1190,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26">
         <v>116.8</v>
@@ -1199,7 +1210,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27">
         <v>122.7</v>
@@ -1219,7 +1230,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28">
         <v>128.69999999999999</v>
@@ -1243,7 +1254,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29">
         <v>135.19999999999999</v>
@@ -1270,7 +1281,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>139.19999999999999</v>
@@ -1297,7 +1308,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B31">
         <v>143.69999999999999</v>
@@ -1324,7 +1335,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32">
         <v>147.19999999999999</v>
@@ -1351,7 +1362,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B33">
         <v>151.5</v>
@@ -1378,7 +1389,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B34">
         <v>155.80000000000001</v>
@@ -1405,7 +1416,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B35">
         <v>159.9</v>
@@ -1432,7 +1443,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B36">
         <v>162.30000000000001</v>
@@ -1459,7 +1470,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B37">
         <v>165.4</v>
@@ -1486,7 +1497,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B38">
         <v>170.8</v>
@@ -1513,7 +1524,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>176.6</v>
@@ -1540,7 +1551,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B40">
         <v>178.9</v>
@@ -1567,7 +1578,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B41">
         <v>183.3</v>
@@ -1594,7 +1605,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B42">
         <v>187.6</v>
@@ -1621,7 +1632,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43">
         <v>193.2</v>
@@ -1648,7 +1659,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B44">
         <v>200.6</v>
@@ -1675,7 +1686,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B45">
         <v>205.709</v>
@@ -1702,7 +1713,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B46">
         <v>214.429</v>
@@ -1729,7 +1740,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B47">
         <v>213.13900000000001</v>
@@ -1756,7 +1767,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B48">
         <v>217.535</v>
@@ -1783,7 +1794,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B49">
         <v>223.59800000000001</v>
@@ -1810,7 +1821,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B50">
         <v>228.85</v>
@@ -1837,7 +1848,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B51">
         <v>232.36600000000001</v>
@@ -1864,7 +1875,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B52">
         <v>236.38399999999999</v>
@@ -1891,7 +1902,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B53">
         <v>236.26499999999999</v>
@@ -1918,7 +1929,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B54">
         <v>238.77799999999999</v>
@@ -1945,7 +1956,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B55">
         <v>244.07599999999999</v>
@@ -1972,7 +1983,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B56">
         <v>250.089</v>
@@ -1996,6 +2007,78 @@
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
       <c r="O56" s="4"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57">
+        <v>254.41200000000001</v>
+      </c>
+      <c r="C57">
+        <v>256.90300000000002</v>
+      </c>
+      <c r="D57">
+        <v>255.65700000000001</v>
+      </c>
+      <c r="E57">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F57">
+        <v>1.8</v>
+      </c>
+      <c r="G57" s="6">
+        <f>$D$50/D57</f>
+        <v>0.89805481563188172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58">
+        <v>257.55700000000002</v>
+      </c>
+      <c r="C58">
+        <v>260.065</v>
+      </c>
+      <c r="D58">
+        <v>258.81099999999998</v>
+      </c>
+      <c r="E58">
+        <v>1.4</v>
+      </c>
+      <c r="F58">
+        <v>1.2</v>
+      </c>
+      <c r="G58" s="6">
+        <f>$D$50/D58</f>
+        <v>0.88711067149387013</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>75</v>
+      </c>
+      <c r="B59">
+        <v>266.23599999999999</v>
+      </c>
+      <c r="C59">
+        <v>275.70299999999997</v>
+      </c>
+      <c r="D59">
+        <v>270.97000000000003</v>
+      </c>
+      <c r="E59">
+        <v>7</v>
+      </c>
+      <c r="F59">
+        <v>4.7</v>
+      </c>
+      <c r="G59" s="6">
+        <f>$D$50/D59</f>
+        <v>0.84730412960844359</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2004,49 +2087,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2054,24 +2120,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -2090,70 +2217,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -2255,40 +2335,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E949DEBD-0B1B-4DE7-9014-907C039D2707}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F45F61B6-7E4B-48E9-BAD9-1BD93FF73237}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00FE6AAB-0D3F-4DF8-84ED-722C1AA7E9D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{054D27E8-3E93-47EA-9C41-623624A49A4F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A822564C-8879-43D9-9576-D5E557518B92}"/>
 </file>